--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/159.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/159.xlsx
@@ -426,13 +426,13 @@
         <v>-15.31417664257183</v>
       </c>
       <c r="E2">
-        <v>-10.57253071598742</v>
+        <v>-7.487983288032791</v>
       </c>
       <c r="F2">
-        <v>-1.106880424183479</v>
+        <v>-0.9810043106125212</v>
       </c>
       <c r="G2">
-        <v>-12.94819693222918</v>
+        <v>-11.36121740652321</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.60066134074491</v>
       </c>
       <c r="E3">
-        <v>-11.25312413154821</v>
+        <v>-8.356843481988472</v>
       </c>
       <c r="F3">
-        <v>-1.126697336303373</v>
+        <v>-1.331406371080119</v>
       </c>
       <c r="G3">
-        <v>-12.60141066589945</v>
+        <v>-11.48808744322471</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.74590921633731</v>
       </c>
       <c r="E4">
-        <v>-12.03949364298017</v>
+        <v>-8.922617439084783</v>
       </c>
       <c r="F4">
-        <v>-1.023257584436446</v>
+        <v>-0.9212692990410184</v>
       </c>
       <c r="G4">
-        <v>-12.04413329309177</v>
+        <v>-10.71224123282327</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.82582799877363</v>
       </c>
       <c r="E5">
-        <v>-12.24698379353762</v>
+        <v>-9.899771560459893</v>
       </c>
       <c r="F5">
-        <v>-0.904044913504699</v>
+        <v>-0.6961827202503138</v>
       </c>
       <c r="G5">
-        <v>-11.9804052914608</v>
+        <v>-11.12464251174136</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.85553940053282</v>
       </c>
       <c r="E6">
-        <v>-12.49980849738585</v>
+        <v>-10.8242006589637</v>
       </c>
       <c r="F6">
-        <v>-0.4657265865533117</v>
+        <v>-0.4762954479799968</v>
       </c>
       <c r="G6">
-        <v>-11.84038907842286</v>
+        <v>-10.28945477254848</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.8563621387787</v>
       </c>
       <c r="E7">
-        <v>-13.77330595782291</v>
+        <v>-10.40717348759733</v>
       </c>
       <c r="F7">
-        <v>-0.24667788656522</v>
+        <v>-0.4498222198975111</v>
       </c>
       <c r="G7">
-        <v>-11.53019096139315</v>
+        <v>-10.55202076035916</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.856859613936162</v>
       </c>
       <c r="E8">
-        <v>-13.2084784517942</v>
+        <v>-11.78863429685126</v>
       </c>
       <c r="F8">
-        <v>-0.04347812352588852</v>
+        <v>-0.04945898891554559</v>
       </c>
       <c r="G8">
-        <v>-11.9956967013067</v>
+        <v>-10.51452552158137</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.870889577365711</v>
       </c>
       <c r="E9">
-        <v>-14.24099316791308</v>
+        <v>-11.96591046882953</v>
       </c>
       <c r="F9">
-        <v>0.23584246433904</v>
+        <v>0.2818024018580504</v>
       </c>
       <c r="G9">
-        <v>-11.72151400919872</v>
+        <v>-9.664039751451526</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.929686270194984</v>
       </c>
       <c r="E10">
-        <v>-15.30984435946951</v>
+        <v>-12.41489055279402</v>
       </c>
       <c r="F10">
-        <v>0.5018844699559665</v>
+        <v>0.2780165528671925</v>
       </c>
       <c r="G10">
-        <v>-10.5932635366874</v>
+        <v>-8.182285915711294</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.041739299218781</v>
       </c>
       <c r="E11">
-        <v>-16.01967360322382</v>
+        <v>-14.27566769338981</v>
       </c>
       <c r="F11">
-        <v>0.6499815612264555</v>
+        <v>0.6605116218582123</v>
       </c>
       <c r="G11">
-        <v>-10.99042637448822</v>
+        <v>-8.523348248803629</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.235558146955577</v>
       </c>
       <c r="E12">
-        <v>-15.43741600073959</v>
+        <v>-15.4819942988711</v>
       </c>
       <c r="F12">
-        <v>0.8609818677522839</v>
+        <v>0.5268246707123069</v>
       </c>
       <c r="G12">
-        <v>-10.01669892556793</v>
+        <v>-9.737033970046918</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.511897187511915</v>
       </c>
       <c r="E13">
-        <v>-16.13586066083862</v>
+        <v>-15.18354069092157</v>
       </c>
       <c r="F13">
-        <v>1.219062526350889</v>
+        <v>1.036382049004949</v>
       </c>
       <c r="G13">
-        <v>-10.27723554896303</v>
+        <v>-7.972423812885814</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.892333433536145</v>
       </c>
       <c r="E14">
-        <v>-17.57102917182352</v>
+        <v>-16.68089873545381</v>
       </c>
       <c r="F14">
-        <v>1.266025741567331</v>
+        <v>1.130527030854162</v>
       </c>
       <c r="G14">
-        <v>-9.640968559588346</v>
+        <v>-8.315445988937398</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.372510591960822</v>
       </c>
       <c r="E15">
-        <v>-19.0572018855568</v>
+        <v>-16.77449323624434</v>
       </c>
       <c r="F15">
-        <v>1.484640506134592</v>
+        <v>1.293046931896559</v>
       </c>
       <c r="G15">
-        <v>-8.822505696459869</v>
+        <v>-7.459408433938194</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.963951775284749</v>
       </c>
       <c r="E16">
-        <v>-19.29352030164708</v>
+        <v>-17.79262099044085</v>
       </c>
       <c r="F16">
-        <v>1.734479616530658</v>
+        <v>1.769541281792571</v>
       </c>
       <c r="G16">
-        <v>-9.113380159176854</v>
+        <v>-6.509920799456443</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.658474770342318</v>
       </c>
       <c r="E17">
-        <v>-19.4998692767546</v>
+        <v>-19.50027683941529</v>
       </c>
       <c r="F17">
-        <v>2.180292831726862</v>
+        <v>2.026100056387846</v>
       </c>
       <c r="G17">
-        <v>-8.847629426557399</v>
+        <v>-7.611157220367306</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.455441638707944</v>
       </c>
       <c r="E18">
-        <v>-20.91462795538693</v>
+        <v>-19.65410004450784</v>
       </c>
       <c r="F18">
-        <v>2.338288084968847</v>
+        <v>2.10062133823885</v>
       </c>
       <c r="G18">
-        <v>-8.691080349096342</v>
+        <v>-6.109265336111686</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.339338478513764</v>
       </c>
       <c r="E19">
-        <v>-21.72743469807566</v>
+        <v>-19.64157428540262</v>
       </c>
       <c r="F19">
-        <v>2.625456727497736</v>
+        <v>2.739043283164884</v>
       </c>
       <c r="G19">
-        <v>-8.872577697741345</v>
+        <v>-6.786765170177995</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.297329608076596</v>
       </c>
       <c r="E20">
-        <v>-21.92080053820319</v>
+        <v>-21.2994259772407</v>
       </c>
       <c r="F20">
-        <v>3.092699067435752</v>
+        <v>3.081507017731341</v>
       </c>
       <c r="G20">
-        <v>-7.897718042246621</v>
+        <v>-6.397491362397253</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.309602208563412</v>
       </c>
       <c r="E21">
-        <v>-22.6432642244389</v>
+        <v>-21.86437575206761</v>
       </c>
       <c r="F21">
-        <v>2.924129409796377</v>
+        <v>2.900069749529021</v>
       </c>
       <c r="G21">
-        <v>-8.052257618565339</v>
+        <v>-5.659885263519937</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.356596762529181</v>
       </c>
       <c r="E22">
-        <v>-23.17175525503006</v>
+        <v>-21.67180239489143</v>
       </c>
       <c r="F22">
-        <v>2.941284112272417</v>
+        <v>3.274372307819473</v>
       </c>
       <c r="G22">
-        <v>-7.647420936204483</v>
+        <v>-4.940295153467334</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.418999725393539</v>
       </c>
       <c r="E23">
-        <v>-24.21257972095302</v>
+        <v>-22.33937644768017</v>
       </c>
       <c r="F23">
-        <v>3.289438102193048</v>
+        <v>2.972627236044879</v>
       </c>
       <c r="G23">
-        <v>-7.20800560568594</v>
+        <v>-5.040137896386214</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.478224683305994</v>
       </c>
       <c r="E24">
-        <v>-23.57665970147789</v>
+        <v>-23.33086771776357</v>
       </c>
       <c r="F24">
-        <v>3.608358464620582</v>
+        <v>3.238113360885487</v>
       </c>
       <c r="G24">
-        <v>-6.712105747176351</v>
+        <v>-5.042322856442133</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.523423815097524</v>
       </c>
       <c r="E25">
-        <v>-24.38836602498277</v>
+        <v>-23.12902004581968</v>
       </c>
       <c r="F25">
-        <v>3.539707980598113</v>
+        <v>3.564052707930248</v>
       </c>
       <c r="G25">
-        <v>-7.036039317648497</v>
+        <v>-5.234225249717065</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.544644092008372</v>
       </c>
       <c r="E26">
-        <v>-24.23114193591046</v>
+        <v>-24.22515076479831</v>
       </c>
       <c r="F26">
-        <v>3.338479139570546</v>
+        <v>3.287045122554819</v>
       </c>
       <c r="G26">
-        <v>-6.644676555632476</v>
+        <v>-4.923888089774706</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.544802684162059</v>
       </c>
       <c r="E27">
-        <v>-24.65395649705862</v>
+        <v>-23.39643549292063</v>
       </c>
       <c r="F27">
-        <v>3.282732691347078</v>
+        <v>3.06077947471007</v>
       </c>
       <c r="G27">
-        <v>-6.702604481478643</v>
+        <v>-5.08771043578554</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.525516131554467</v>
       </c>
       <c r="E28">
-        <v>-25.14405512501276</v>
+        <v>-23.3046750241032</v>
       </c>
       <c r="F28">
-        <v>3.037720716581271</v>
+        <v>3.161599776992861</v>
       </c>
       <c r="G28">
-        <v>-5.526672221565203</v>
+        <v>-5.054419589842629</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.501593741754795</v>
       </c>
       <c r="E29">
-        <v>-23.83248678359321</v>
+        <v>-23.85532387801389</v>
       </c>
       <c r="F29">
-        <v>2.872535438483191</v>
+        <v>3.00964161070053</v>
       </c>
       <c r="G29">
-        <v>-6.579376044870352</v>
+        <v>-5.638773914616005</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.481461640340751</v>
       </c>
       <c r="E30">
-        <v>-24.25246199153857</v>
+        <v>-23.48378975652859</v>
       </c>
       <c r="F30">
-        <v>3.044581330606955</v>
+        <v>2.925901576715754</v>
       </c>
       <c r="G30">
-        <v>-6.117988623607665</v>
+        <v>-4.727781303664898</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.485505847769491</v>
       </c>
       <c r="E31">
-        <v>-24.18194459429113</v>
+        <v>-23.10114275982846</v>
       </c>
       <c r="F31">
-        <v>3.157119472958082</v>
+        <v>3.003146832741313</v>
       </c>
       <c r="G31">
-        <v>-6.628819042499367</v>
+        <v>-4.931068663049385</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.523306356169291</v>
       </c>
       <c r="E32">
-        <v>-24.15337898025074</v>
+        <v>-22.31723220978267</v>
       </c>
       <c r="F32">
-        <v>2.89965006746143</v>
+        <v>2.964144907161785</v>
       </c>
       <c r="G32">
-        <v>-6.607701072504356</v>
+        <v>-5.227412146997245</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.615685525099803</v>
       </c>
       <c r="E33">
-        <v>-23.33398330788085</v>
+        <v>-22.25743823898539</v>
       </c>
       <c r="F33">
-        <v>3.043064140339964</v>
+        <v>3.153719256357634</v>
       </c>
       <c r="G33">
-        <v>-6.809588071125731</v>
+        <v>-5.098333976421062</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.768529848325243</v>
       </c>
       <c r="E34">
-        <v>-22.73353029683379</v>
+        <v>-22.71579679261976</v>
       </c>
       <c r="F34">
-        <v>2.728030192228919</v>
+        <v>2.975335373160281</v>
       </c>
       <c r="G34">
-        <v>-6.33350513821422</v>
+        <v>-4.814332206243604</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.997870981522817</v>
       </c>
       <c r="E35">
-        <v>-22.03473694423617</v>
+        <v>-21.2601641075942</v>
       </c>
       <c r="F35">
-        <v>2.609709939580522</v>
+        <v>2.610397267947822</v>
       </c>
       <c r="G35">
-        <v>-6.627263086095909</v>
+        <v>-5.353884918234022</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.301600139284349</v>
       </c>
       <c r="E36">
-        <v>-22.94114724466345</v>
+        <v>-22.19320183518658</v>
       </c>
       <c r="F36">
-        <v>2.671219493630275</v>
+        <v>2.670872662034793</v>
       </c>
       <c r="G36">
-        <v>-7.154881281417255</v>
+        <v>-4.939186120711677</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.68784203640379</v>
       </c>
       <c r="E37">
-        <v>-21.18229699703231</v>
+        <v>-20.12664630720824</v>
       </c>
       <c r="F37">
-        <v>2.746092358194505</v>
+        <v>2.429371763283517</v>
       </c>
       <c r="G37">
-        <v>-7.155387794884764</v>
+        <v>-4.963651052246892</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.146715264726064</v>
       </c>
       <c r="E38">
-        <v>-21.94015070763796</v>
+        <v>-20.01994640263951</v>
       </c>
       <c r="F38">
-        <v>2.704942927393642</v>
+        <v>2.361134626504977</v>
       </c>
       <c r="G38">
-        <v>-7.15181240570235</v>
+        <v>-5.673514779505116</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.679296336935268</v>
       </c>
       <c r="E39">
-        <v>-20.88073685591352</v>
+        <v>-20.04498886390192</v>
       </c>
       <c r="F39">
-        <v>2.805677709556999</v>
+        <v>3.027429795542746</v>
       </c>
       <c r="G39">
-        <v>-7.15299427045987</v>
+        <v>-4.606919907117186</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.269048368137287</v>
       </c>
       <c r="E40">
-        <v>-20.58811139401187</v>
+        <v>-19.94977769789066</v>
       </c>
       <c r="F40">
-        <v>2.452622149828083</v>
+        <v>2.78776916306521</v>
       </c>
       <c r="G40">
-        <v>-7.211657137415756</v>
+        <v>-4.688356016837718</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.90931205560826</v>
       </c>
       <c r="E41">
-        <v>-20.22247334568455</v>
+        <v>-20.02153136854219</v>
       </c>
       <c r="F41">
-        <v>2.698476656140903</v>
+        <v>2.46109972759343</v>
       </c>
       <c r="G41">
-        <v>-6.9159294149382</v>
+        <v>-5.061845143487215</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.577109876158214</v>
       </c>
       <c r="E42">
-        <v>-20.51917896266711</v>
+        <v>-18.79460926327403</v>
       </c>
       <c r="F42">
-        <v>2.799536098016925</v>
+        <v>2.429123121454793</v>
       </c>
       <c r="G42">
-        <v>-7.39673980687979</v>
+        <v>-4.749922232231544</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.25872060609141</v>
       </c>
       <c r="E43">
-        <v>-18.97868720321182</v>
+        <v>-18.47973088009868</v>
       </c>
       <c r="F43">
-        <v>2.674483511521995</v>
+        <v>2.767721029881662</v>
       </c>
       <c r="G43">
-        <v>-6.954695903203065</v>
+        <v>-4.510053344638111</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.927052860420346</v>
       </c>
       <c r="E44">
-        <v>-17.64367948032857</v>
+        <v>-17.81128283182646</v>
       </c>
       <c r="F44">
-        <v>2.852628255126117</v>
+        <v>2.420805497986905</v>
       </c>
       <c r="G44">
-        <v>-6.944297479664215</v>
+        <v>-4.6151234389635</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.564831825284054</v>
       </c>
       <c r="E45">
-        <v>-18.89757317678643</v>
+        <v>-17.45843772257081</v>
       </c>
       <c r="F45">
-        <v>2.892645336197441</v>
+        <v>2.632567567058059</v>
       </c>
       <c r="G45">
-        <v>-7.300237404410035</v>
+        <v>-4.36797135118367</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.14632681500494</v>
       </c>
       <c r="E46">
-        <v>-17.81170850838318</v>
+        <v>-16.16167296268234</v>
       </c>
       <c r="F46">
-        <v>3.045617074275652</v>
+        <v>2.532817849974106</v>
       </c>
       <c r="G46">
-        <v>-7.053184632996383</v>
+        <v>-4.600874850962477</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.65798452535445</v>
       </c>
       <c r="E47">
-        <v>-16.85105614629202</v>
+        <v>-16.49725100054674</v>
       </c>
       <c r="F47">
-        <v>2.772662192337833</v>
+        <v>2.147601974220361</v>
       </c>
       <c r="G47">
-        <v>-7.976995676275547</v>
+        <v>-5.720491420707375</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.08413755884954</v>
       </c>
       <c r="E48">
-        <v>-17.00977010331285</v>
+        <v>-15.3092466009005</v>
       </c>
       <c r="F48">
-        <v>2.489500325775006</v>
+        <v>2.433193245657472</v>
       </c>
       <c r="G48">
-        <v>-7.153490852290761</v>
+        <v>-5.472409069631009</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.42050324729816</v>
       </c>
       <c r="E49">
-        <v>-15.76495599724038</v>
+        <v>-14.05480495908771</v>
       </c>
       <c r="F49">
-        <v>2.440706346520316</v>
+        <v>2.089475216005987</v>
       </c>
       <c r="G49">
-        <v>-6.990138603746503</v>
+        <v>-5.776224454861005</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.66291036645946</v>
       </c>
       <c r="E50">
-        <v>-15.08242892327831</v>
+        <v>-14.25365025276452</v>
       </c>
       <c r="F50">
-        <v>2.671338271573933</v>
+        <v>2.698782311382583</v>
       </c>
       <c r="G50">
-        <v>-7.47405097685839</v>
+        <v>-5.881205164456834</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.8160181434643</v>
       </c>
       <c r="E51">
-        <v>-15.37474192047343</v>
+        <v>-14.09838699293753</v>
       </c>
       <c r="F51">
-        <v>2.510558863332604</v>
+        <v>1.935843072561037</v>
       </c>
       <c r="G51">
-        <v>-7.359420027015586</v>
+        <v>-5.371394393591228</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.88633939565426</v>
       </c>
       <c r="E52">
-        <v>-15.69361441772354</v>
+        <v>-14.57194763381565</v>
       </c>
       <c r="F52">
-        <v>2.048379631206249</v>
+        <v>2.11903983803541</v>
       </c>
       <c r="G52">
-        <v>-7.290514332161195</v>
+        <v>-5.802288379891687</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.8835319936244</v>
       </c>
       <c r="E53">
-        <v>-15.22899298453656</v>
+        <v>-14.19077239116802</v>
       </c>
       <c r="F53">
-        <v>2.355116544026307</v>
+        <v>2.031654113033293</v>
       </c>
       <c r="G53">
-        <v>-6.911407209731555</v>
+        <v>-5.002304981963422</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.81919141941489</v>
       </c>
       <c r="E54">
-        <v>-13.84401807945268</v>
+        <v>-13.78373956193658</v>
       </c>
       <c r="F54">
-        <v>2.132091158484547</v>
+        <v>2.023072010677526</v>
       </c>
       <c r="G54">
-        <v>-7.825806372042572</v>
+        <v>-5.351458288353736</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.70245277594722</v>
       </c>
       <c r="E55">
-        <v>-13.99752429136469</v>
+        <v>-12.42961715026696</v>
       </c>
       <c r="F55">
-        <v>1.996913940072213</v>
+        <v>1.7719136732539</v>
       </c>
       <c r="G55">
-        <v>-7.065443583128305</v>
+        <v>-4.884661435679881</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.54606851199689</v>
       </c>
       <c r="E56">
-        <v>-13.88459773503542</v>
+        <v>-11.78568626027227</v>
       </c>
       <c r="F56">
-        <v>2.348689865421454</v>
+        <v>1.684231795245595</v>
       </c>
       <c r="G56">
-        <v>-7.667337178168738</v>
+        <v>-5.60672121270478</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.35534683346658</v>
       </c>
       <c r="E57">
-        <v>-13.89969566737699</v>
+        <v>-11.8442122583474</v>
       </c>
       <c r="F57">
-        <v>2.198814272407926</v>
+        <v>2.140527559896093</v>
       </c>
       <c r="G57">
-        <v>-7.841230203710036</v>
+        <v>-5.447364792626423</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.14195414000946</v>
       </c>
       <c r="E58">
-        <v>-13.34568668575261</v>
+        <v>-11.57077394081625</v>
       </c>
       <c r="F58">
-        <v>2.014067058842337</v>
+        <v>2.08100080565247</v>
       </c>
       <c r="G58">
-        <v>-7.959919882383987</v>
+        <v>-6.364690477194155</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.90614037345521</v>
       </c>
       <c r="E59">
-        <v>-13.62518410150602</v>
+        <v>-10.30719383845599</v>
       </c>
       <c r="F59">
-        <v>2.056190468781196</v>
+        <v>1.885620590570621</v>
       </c>
       <c r="G59">
-        <v>-7.407856618800663</v>
+        <v>-5.531485754779304</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.65912827375256</v>
       </c>
       <c r="E60">
-        <v>-14.14786962841935</v>
+        <v>-10.51804411672713</v>
       </c>
       <c r="F60">
-        <v>1.749724369672678</v>
+        <v>1.649904969528445</v>
       </c>
       <c r="G60">
-        <v>-7.965362419250549</v>
+        <v>-6.116704131938429</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.39763341239235</v>
       </c>
       <c r="E61">
-        <v>-13.31751504895089</v>
+        <v>-10.49721313629184</v>
       </c>
       <c r="F61">
-        <v>1.796584644004615</v>
+        <v>1.896769880215315</v>
       </c>
       <c r="G61">
-        <v>-7.564706955905792</v>
+        <v>-6.822674657642469</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.13206246406525</v>
       </c>
       <c r="E62">
-        <v>-12.52179423869309</v>
+        <v>-10.57828640645117</v>
       </c>
       <c r="F62">
-        <v>1.684356908012914</v>
+        <v>1.459705056495998</v>
       </c>
       <c r="G62">
-        <v>-7.782881838580382</v>
+        <v>-6.218877498916955</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.856309918632071</v>
       </c>
       <c r="E63">
-        <v>-12.49477736276333</v>
+        <v>-11.30543706328482</v>
       </c>
       <c r="F63">
-        <v>1.631817464268211</v>
+        <v>1.359996515765846</v>
       </c>
       <c r="G63">
-        <v>-7.433546452185407</v>
+        <v>-6.951921666041156</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.577850761293442</v>
       </c>
       <c r="E64">
-        <v>-11.99467986420026</v>
+        <v>-9.142583535533364</v>
       </c>
       <c r="F64">
-        <v>1.524811206679714</v>
+        <v>1.222771565604849</v>
       </c>
       <c r="G64">
-        <v>-7.514264173523917</v>
+        <v>-4.85505191637664</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.286906522210206</v>
       </c>
       <c r="E65">
-        <v>-11.19681255726283</v>
+        <v>-9.706546103026607</v>
       </c>
       <c r="F65">
-        <v>1.501448377015151</v>
+        <v>1.321677167435873</v>
       </c>
       <c r="G65">
-        <v>-7.401702314643158</v>
+        <v>-5.786007116929551</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.98823389951635</v>
       </c>
       <c r="E66">
-        <v>-11.95386925644314</v>
+        <v>-10.72427535151044</v>
       </c>
       <c r="F66">
-        <v>1.454670455390816</v>
+        <v>1.127853735268901</v>
       </c>
       <c r="G66">
-        <v>-7.031454212076607</v>
+        <v>-6.557437059581602</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.670549197148361</v>
       </c>
       <c r="E67">
-        <v>-12.38284707071574</v>
+        <v>-9.991930534989992</v>
       </c>
       <c r="F67">
-        <v>1.711823119704381</v>
+        <v>1.5282050884565</v>
       </c>
       <c r="G67">
-        <v>-8.040875963001325</v>
+        <v>-5.554325208454736</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.338369440154477</v>
       </c>
       <c r="E68">
-        <v>-11.76624552135734</v>
+        <v>-8.717409639427201</v>
       </c>
       <c r="F68">
-        <v>1.289241286581758</v>
+        <v>0.7794320990485605</v>
       </c>
       <c r="G68">
-        <v>-7.147826508873068</v>
+        <v>-6.186354699539155</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.9812781975808</v>
       </c>
       <c r="E69">
-        <v>-12.21036655271159</v>
+        <v>-9.69753896822535</v>
       </c>
       <c r="F69">
-        <v>1.193292463694859</v>
+        <v>1.316881705923922</v>
       </c>
       <c r="G69">
-        <v>-7.053376644637661</v>
+        <v>-5.20331468601689</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.606033903866193</v>
       </c>
       <c r="E70">
-        <v>-11.81574174226118</v>
+        <v>-10.63314886905409</v>
       </c>
       <c r="F70">
-        <v>1.030124826933048</v>
+        <v>0.6867077014054963</v>
       </c>
       <c r="G70">
-        <v>-7.376240908900622</v>
+        <v>-5.568779050279193</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.205463561569382</v>
       </c>
       <c r="E71">
-        <v>-11.30127992414578</v>
+        <v>-9.215953871405638</v>
       </c>
       <c r="F71">
-        <v>1.110385459021604</v>
+        <v>0.8850272746664011</v>
       </c>
       <c r="G71">
-        <v>-6.902236998587775</v>
+        <v>-5.716008942047201</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.790563734114744</v>
       </c>
       <c r="E72">
-        <v>-12.09214621026735</v>
+        <v>-10.61794678181034</v>
       </c>
       <c r="F72">
-        <v>0.9686358610601958</v>
+        <v>0.7819945352197415</v>
       </c>
       <c r="G72">
-        <v>-6.889686720448397</v>
+        <v>-5.14358251285182</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.358690733936552</v>
       </c>
       <c r="E73">
-        <v>-12.20681622908958</v>
+        <v>-9.928658696154823</v>
       </c>
       <c r="F73">
-        <v>0.9051023308505115</v>
+        <v>0.7979931323775108</v>
       </c>
       <c r="G73">
-        <v>-6.396796147834007</v>
+        <v>-5.216040423069849</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.924283796441304</v>
       </c>
       <c r="E74">
-        <v>-11.59165473446562</v>
+        <v>-10.47507795534235</v>
       </c>
       <c r="F74">
-        <v>0.8552013411609299</v>
+        <v>0.5631406310592488</v>
       </c>
       <c r="G74">
-        <v>-6.614461206495548</v>
+        <v>-4.863242206040796</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.487373632314035</v>
       </c>
       <c r="E75">
-        <v>-12.65205579352373</v>
+        <v>-9.990879929020213</v>
       </c>
       <c r="F75">
-        <v>0.5918342148351807</v>
+        <v>0.7115022012176162</v>
       </c>
       <c r="G75">
-        <v>-6.372619233760709</v>
+        <v>-4.588029934270105</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.063925643538496</v>
       </c>
       <c r="E76">
-        <v>-13.24332505928322</v>
+        <v>-10.52168048135529</v>
       </c>
       <c r="F76">
-        <v>0.5998778571796977</v>
+        <v>0.3168038862951777</v>
       </c>
       <c r="G76">
-        <v>-6.032152798865442</v>
+        <v>-5.016414527051796</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.654728814711594</v>
       </c>
       <c r="E77">
-        <v>-13.3005196860001</v>
+        <v>-11.51481105902946</v>
       </c>
       <c r="F77">
-        <v>0.4658931693216896</v>
+        <v>0.7412061893675985</v>
       </c>
       <c r="G77">
-        <v>-6.202473745769867</v>
+        <v>-4.220085971398887</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.275045807207616</v>
       </c>
       <c r="E78">
-        <v>-13.69155341656244</v>
+        <v>-12.11823474902554</v>
       </c>
       <c r="F78">
-        <v>0.415062544259745</v>
+        <v>0.3798591373183993</v>
       </c>
       <c r="G78">
-        <v>-5.134554655166228</v>
+        <v>-4.027316215192665</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.924089840685953</v>
       </c>
       <c r="E79">
-        <v>-14.64769994701596</v>
+        <v>-12.28176247391652</v>
       </c>
       <c r="F79">
-        <v>0.5906448516926857</v>
+        <v>0.2449353118525356</v>
       </c>
       <c r="G79">
-        <v>-5.697224906657376</v>
+        <v>-4.055416125729999</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.613266869280747</v>
       </c>
       <c r="E80">
-        <v>-14.14683260787159</v>
+        <v>-12.64583367023719</v>
       </c>
       <c r="F80">
-        <v>0.3911913449963262</v>
+        <v>0.3391824427332948</v>
       </c>
       <c r="G80">
-        <v>-5.360856927139728</v>
+        <v>-3.852257877621544</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.338908095612948</v>
       </c>
       <c r="E81">
-        <v>-15.23711253843231</v>
+        <v>-13.29340998180806</v>
       </c>
       <c r="F81">
-        <v>0.5239264888870526</v>
+        <v>-0.1098488628830826</v>
       </c>
       <c r="G81">
-        <v>-5.140195824765145</v>
+        <v>-3.145734490812444</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.107597807046544</v>
       </c>
       <c r="E82">
-        <v>-16.54836388667132</v>
+        <v>-13.55327646273822</v>
       </c>
       <c r="F82">
-        <v>0.4554430858386623</v>
+        <v>0.3000474858568706</v>
       </c>
       <c r="G82">
-        <v>-4.864285027885667</v>
+        <v>-2.979935749114665</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.913707927045597</v>
       </c>
       <c r="E83">
-        <v>-17.34551569471554</v>
+        <v>-15.84694854762326</v>
       </c>
       <c r="F83">
-        <v>0.4193385502314316</v>
+        <v>0.05789726768026367</v>
       </c>
       <c r="G83">
-        <v>-4.259584090227931</v>
+        <v>-3.31595612135069</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.758965767493931</v>
       </c>
       <c r="E84">
-        <v>-18.33744169830367</v>
+        <v>-16.54273952195379</v>
       </c>
       <c r="F84">
-        <v>0.2542498781941927</v>
+        <v>-0.0188910891886911</v>
       </c>
       <c r="G84">
-        <v>-3.721060957900227</v>
+        <v>-3.909934202006726</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.6375387449003</v>
       </c>
       <c r="E85">
-        <v>-18.2787753175343</v>
+        <v>-17.51427380708538</v>
       </c>
       <c r="F85">
-        <v>0.2512828051616169</v>
+        <v>0.561278192902692</v>
       </c>
       <c r="G85">
-        <v>-3.892835234296391</v>
+        <v>-3.211051554302265</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.548623684037045</v>
       </c>
       <c r="E86">
-        <v>-20.27360434570516</v>
+        <v>-18.77990530817112</v>
       </c>
       <c r="F86">
-        <v>0.1738791785445139</v>
+        <v>-0.2504478984969236</v>
       </c>
       <c r="G86">
-        <v>-4.101568441092978</v>
+        <v>-2.658107685605495</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.487966231992888</v>
       </c>
       <c r="E87">
-        <v>-22.79741347966</v>
+        <v>-20.67855407689306</v>
       </c>
       <c r="F87">
-        <v>-0.1810435704587053</v>
+        <v>-0.08346511418481913</v>
       </c>
       <c r="G87">
-        <v>-3.787208968320404</v>
+        <v>-2.030520946634777</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.453458565773623</v>
       </c>
       <c r="E88">
-        <v>-23.02151407287758</v>
+        <v>-21.43528925441883</v>
       </c>
       <c r="F88">
-        <v>-0.1974230488891377</v>
+        <v>-0.2646703694705275</v>
       </c>
       <c r="G88">
-        <v>-4.158559482551532</v>
+        <v>-2.098118976001155</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.442797410903875</v>
       </c>
       <c r="E89">
-        <v>-24.25229896647429</v>
+        <v>-23.18471121916601</v>
       </c>
       <c r="F89">
-        <v>-0.19937734198879</v>
+        <v>-0.4105368109591201</v>
       </c>
       <c r="G89">
-        <v>-3.364703904416458</v>
+        <v>-2.839588481522802</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.453017904809625</v>
       </c>
       <c r="E90">
-        <v>-25.07479211506544</v>
+        <v>-24.19694290020453</v>
       </c>
       <c r="F90">
-        <v>-0.0662731946197662</v>
+        <v>-0.193218309683646</v>
       </c>
       <c r="G90">
-        <v>-3.542745043518463</v>
+        <v>-2.694993784004054</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.484206522400588</v>
       </c>
       <c r="E91">
-        <v>-27.84387245822372</v>
+        <v>-26.19399993758716</v>
       </c>
       <c r="F91">
-        <v>-0.2909456343135834</v>
+        <v>-0.3321623726158527</v>
       </c>
       <c r="G91">
-        <v>-3.558195359550242</v>
+        <v>-1.522021151802723</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.533369831825172</v>
       </c>
       <c r="E92">
-        <v>-29.20005985404084</v>
+        <v>-29.38313700122294</v>
       </c>
       <c r="F92">
-        <v>-0.7067895906189695</v>
+        <v>-0.7081088176465306</v>
       </c>
       <c r="G92">
-        <v>-3.740639524219477</v>
+        <v>-2.811005231336734</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.603097018847213</v>
       </c>
       <c r="E93">
-        <v>-31.42565991764258</v>
+        <v>-29.56490994789083</v>
       </c>
       <c r="F93">
-        <v>-0.5518627675881478</v>
+        <v>-0.6329849356947026</v>
       </c>
       <c r="G93">
-        <v>-3.518270180346631</v>
+        <v>-2.113125678930672</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.690702882125586</v>
       </c>
       <c r="E94">
-        <v>-33.34089648665461</v>
+        <v>-32.76702335379559</v>
       </c>
       <c r="F94">
-        <v>-0.67694227708364</v>
+        <v>-0.9573025678820545</v>
       </c>
       <c r="G94">
-        <v>-3.690458274935204</v>
+        <v>-1.320150705909044</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.799583928228155</v>
       </c>
       <c r="E95">
-        <v>-36.32374797381899</v>
+        <v>-34.61380750970768</v>
       </c>
       <c r="F95">
-        <v>-0.5992694204609122</v>
+        <v>-0.6877922463103155</v>
       </c>
       <c r="G95">
-        <v>-3.998123824627372</v>
+        <v>-2.02914707023598</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.930685962915406</v>
       </c>
       <c r="E96">
-        <v>-37.84759532705909</v>
+        <v>-37.51740617326382</v>
       </c>
       <c r="F96">
-        <v>-0.626652487591818</v>
+        <v>-0.576365865511827</v>
       </c>
       <c r="G96">
-        <v>-4.140480593361572</v>
+        <v>-2.063626402027489</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.08430613994296</v>
       </c>
       <c r="E97">
-        <v>-40.65127547587298</v>
+        <v>-39.9909401887855</v>
       </c>
       <c r="F97">
-        <v>-1.038278243191431</v>
+        <v>-0.5357770666050293</v>
       </c>
       <c r="G97">
-        <v>-4.744201609539683</v>
+        <v>-2.943648859458713</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.267338235171382</v>
       </c>
       <c r="E98">
-        <v>-42.81207760489896</v>
+        <v>-41.0727020597378</v>
       </c>
       <c r="F98">
-        <v>-0.9941577800932035</v>
+        <v>-0.4769669392881432</v>
       </c>
       <c r="G98">
-        <v>-4.485561928738583</v>
+        <v>-3.049827986539758</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.46955419158487</v>
       </c>
       <c r="E99">
-        <v>-44.71020333487302</v>
+        <v>-45.03068570463285</v>
       </c>
       <c r="F99">
-        <v>-0.9895618655265983</v>
+        <v>-0.7695708605188201</v>
       </c>
       <c r="G99">
-        <v>-5.179091424306043</v>
+        <v>-2.866493285120459</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.709593204906802</v>
       </c>
       <c r="E100">
-        <v>-47.55428652878334</v>
+        <v>-46.2910687043437</v>
       </c>
       <c r="F100">
-        <v>-1.275585488678624</v>
+        <v>-1.023428624675313</v>
       </c>
       <c r="G100">
-        <v>-4.995167445780754</v>
+        <v>-3.748836434974712</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.952316311423202</v>
       </c>
       <c r="E101">
-        <v>-49.32336773131632</v>
+        <v>-48.59089158904965</v>
       </c>
       <c r="F101">
-        <v>-1.428652249111762</v>
+        <v>-1.041461492081464</v>
       </c>
       <c r="G101">
-        <v>-5.540970467749315</v>
+        <v>-2.93962323608296</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.25287430857669</v>
       </c>
       <c r="E102">
-        <v>-51.1442784509856</v>
+        <v>-50.80792717618438</v>
       </c>
       <c r="F102">
-        <v>-1.466110853276694</v>
+        <v>-1.156590577310251</v>
       </c>
       <c r="G102">
-        <v>-5.756609472540823</v>
+        <v>-2.897526339005587</v>
       </c>
     </row>
   </sheetData>
